--- a/example xl/agriledger back new.xlsx
+++ b/example xl/agriledger back new.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BE1C94-F796-48B0-95A1-9A7089A7216E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832AC5D6-BBEE-4CA4-BBE8-677869015319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FINANCIAL STATEMENT" sheetId="1" r:id="rId1"/>
@@ -24,13 +24,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'INVENTORY APRIL 30 2026'!$A$1:$M$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MARCH SALES'!$G$1:$G$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PURCHASES  2026'!$A$1:$L$229</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PURCHASES APRIL 2026'!$A$1:$L$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PURCHASES FEB 2026'!$A$1:$L$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'PURCHASES JAN 2026'!$A$1:$L$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PURCHASES MARCH 2026'!$A$1:$L$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SALES 2026'!$A$1:$AA$743</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SALES JAN 2026'!$A$1:$AA$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SALES FEB 2026'!$G$1:$G$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SALES JAN 2026'!$A$1:$AA$187</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36759,6 +36761,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60ED403F-78CB-6D47-BB80-6E9874AF083C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X178"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -36839,7 +36842,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>46082</v>
       </c>
@@ -36883,7 +36886,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>46082</v>
       </c>
@@ -36925,7 +36928,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>46082</v>
       </c>
@@ -36969,7 +36972,7 @@
         <v>542.97</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>46082</v>
       </c>
@@ -37011,7 +37014,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46083</v>
       </c>
@@ -37053,7 +37056,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>46083</v>
       </c>
@@ -37095,7 +37098,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>46083</v>
       </c>
@@ -37137,7 +37140,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>46083</v>
       </c>
@@ -37179,7 +37182,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>46083</v>
       </c>
@@ -37221,7 +37224,7 @@
         <v>22776.9</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>46083</v>
       </c>
@@ -37303,7 +37306,7 @@
         <v>6413.05</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>46083</v>
       </c>
@@ -37345,7 +37348,7 @@
         <v>101846</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>46084</v>
       </c>
@@ -37387,7 +37390,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46084</v>
       </c>
@@ -37429,7 +37432,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>46084</v>
       </c>
@@ -37471,7 +37474,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>46084</v>
       </c>
@@ -37513,7 +37516,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46084</v>
       </c>
@@ -37557,7 +37560,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46085</v>
       </c>
@@ -37599,7 +37602,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>46085</v>
       </c>
@@ -37641,7 +37644,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>46085</v>
       </c>
@@ -37685,7 +37688,7 @@
         <v>2685.52</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>46085</v>
       </c>
@@ -37729,7 +37732,7 @@
         <v>268.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46085</v>
       </c>
@@ -37773,7 +37776,7 @@
         <v>295.32</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46085</v>
       </c>
@@ -37817,7 +37820,7 @@
         <v>266.67</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>46085</v>
       </c>
@@ -37861,7 +37864,7 @@
         <v>1325.37</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46085</v>
       </c>
@@ -37905,7 +37908,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46085</v>
       </c>
@@ -37949,7 +37952,7 @@
         <v>142.66</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46085</v>
       </c>
@@ -37989,7 +37992,7 @@
         <v>3588.16</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>46085</v>
       </c>
@@ -38031,7 +38034,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>46085</v>
       </c>
@@ -38073,7 +38076,7 @@
         <v>1030.1400000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>46085</v>
       </c>
@@ -38115,7 +38118,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>46086</v>
       </c>
@@ -38157,7 +38160,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46086</v>
       </c>
@@ -38199,7 +38202,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>46086</v>
       </c>
@@ -38241,7 +38244,7 @@
         <v>515.07000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46086</v>
       </c>
@@ -38285,7 +38288,7 @@
         <v>588.34</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46086</v>
       </c>
@@ -38327,7 +38330,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46086</v>
       </c>
@@ -38371,7 +38374,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46086</v>
       </c>
@@ -38415,7 +38418,7 @@
         <v>142.66</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46086</v>
       </c>
@@ -38461,7 +38464,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>46086</v>
       </c>
@@ -38509,7 +38512,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>46086</v>
       </c>
@@ -38555,7 +38558,7 @@
         <v>285.32</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>46087</v>
       </c>
@@ -38597,7 +38600,7 @@
         <v>17684.599999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>46087</v>
       </c>
@@ -38639,7 +38642,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>46087</v>
       </c>
@@ -38723,7 +38726,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>46087</v>
       </c>
@@ -38759,7 +38762,7 @@
         <v>-4083.31</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46087</v>
       </c>
@@ -38801,7 +38804,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46087</v>
       </c>
@@ -38843,7 +38846,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46087</v>
       </c>
@@ -38883,7 +38886,7 @@
         <v>1654.08</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46087</v>
       </c>
@@ -38925,7 +38928,7 @@
         <v>1974.08</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46088</v>
       </c>
@@ -38969,7 +38972,7 @@
         <v>542.97</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>46088</v>
       </c>
@@ -39013,7 +39016,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>46090</v>
       </c>
@@ -39055,7 +39058,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>46090</v>
       </c>
@@ -39097,7 +39100,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>46090</v>
       </c>
@@ -39141,7 +39144,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>46090</v>
       </c>
@@ -39185,7 +39188,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>46090</v>
       </c>
@@ -39227,7 +39230,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>46090</v>
       </c>
@@ -39269,7 +39272,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>46090</v>
       </c>
@@ -39313,7 +39316,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>46090</v>
       </c>
@@ -39357,7 +39360,7 @@
         <v>341.44</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>46090</v>
       </c>
@@ -39401,7 +39404,7 @@
         <v>1325.37</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>46091</v>
       </c>
@@ -39443,7 +39446,7 @@
         <v>858.45</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>46091</v>
       </c>
@@ -39485,7 +39488,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>46091</v>
       </c>
@@ -39527,7 +39530,7 @@
         <v>887.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>46092</v>
       </c>
@@ -39569,7 +39572,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>46092</v>
       </c>
@@ -39611,7 +39614,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>46092</v>
       </c>
@@ -39653,7 +39656,7 @@
         <v>3308.16</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>46092</v>
       </c>
@@ -39695,7 +39698,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>46092</v>
       </c>
@@ -39737,7 +39740,7 @@
         <v>6342.3</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>46092</v>
       </c>
@@ -39781,7 +39784,7 @@
         <v>682.88</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>46092</v>
       </c>
@@ -39825,7 +39828,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>46092</v>
       </c>
@@ -39867,7 +39870,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>46092</v>
       </c>
@@ -39913,7 +39916,7 @@
         <v>26792.59</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>46092</v>
       </c>
@@ -39955,7 +39958,7 @@
         <v>515.07000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>46092</v>
       </c>
@@ -39997,7 +40000,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>46092</v>
       </c>
@@ -40037,7 +40040,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26">
         <v>46092</v>
       </c>
@@ -40121,7 +40124,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="26">
         <v>46092</v>
       </c>
@@ -40161,7 +40164,7 @@
         <v>-423.4</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>46093</v>
       </c>
@@ -40203,7 +40206,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>46093</v>
       </c>
@@ -40245,7 +40248,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>46093</v>
       </c>
@@ -40327,7 +40330,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>46093</v>
       </c>
@@ -40369,7 +40372,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>46093</v>
       </c>
@@ -40411,7 +40414,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>46093</v>
       </c>
@@ -40493,7 +40496,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>46094</v>
       </c>
@@ -40535,7 +40538,7 @@
         <v>15184.6</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>46094</v>
       </c>
@@ -40577,7 +40580,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>46094</v>
       </c>
@@ -40621,7 +40624,7 @@
         <v>1176.68</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>46094</v>
       </c>
@@ -40663,7 +40666,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>46094</v>
       </c>
@@ -40705,7 +40708,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>46094</v>
       </c>
@@ -40749,7 +40752,7 @@
         <v>1085.94</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>46094</v>
       </c>
@@ -40791,7 +40794,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>46095</v>
       </c>
@@ -40833,7 +40836,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>46095</v>
       </c>
@@ -40877,7 +40880,7 @@
         <v>260.8</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>46095</v>
       </c>
@@ -40919,7 +40922,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>46095</v>
       </c>
@@ -40961,7 +40964,7 @@
         <v>7592.3</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>46095</v>
       </c>
@@ -41003,7 +41006,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>46095</v>
       </c>
@@ -41045,7 +41048,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>46095</v>
       </c>
@@ -41087,7 +41090,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>46095</v>
       </c>
@@ -41129,7 +41132,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>46097</v>
       </c>
@@ -41171,7 +41174,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>46097</v>
       </c>
@@ -41215,7 +41218,7 @@
         <v>882.51</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>46097</v>
       </c>
@@ -41257,7 +41260,7 @@
         <v>858.45</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>46097</v>
       </c>
@@ -41341,7 +41344,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>46097</v>
       </c>
@@ -41383,7 +41386,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>46097</v>
       </c>
@@ -41425,7 +41428,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>46097</v>
       </c>
@@ -41467,7 +41470,7 @@
         <v>10629.22</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>46097</v>
       </c>
@@ -41509,7 +41512,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>46097</v>
       </c>
@@ -41551,7 +41554,7 @@
         <v>3588.16</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>46098</v>
       </c>
@@ -41601,7 +41604,7 @@
         <v>3457.96</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>46098</v>
       </c>
@@ -41645,7 +41648,7 @@
         <v>430.64</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>46098</v>
       </c>
@@ -41687,7 +41690,7 @@
         <v>8842.2999999999993</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>46099</v>
       </c>
@@ -41729,7 +41732,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>46099</v>
       </c>
@@ -41773,7 +41776,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>46099</v>
       </c>
@@ -41817,7 +41820,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>46099</v>
       </c>
@@ -41859,7 +41862,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>46100</v>
       </c>
@@ -41903,7 +41906,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>46100</v>
       </c>
@@ -41947,7 +41950,7 @@
         <v>588.34</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>46100</v>
       </c>
@@ -41989,7 +41992,7 @@
         <v>15184.6</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>46101</v>
       </c>
@@ -42031,7 +42034,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>46101</v>
       </c>
@@ -42073,7 +42076,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>46101</v>
       </c>
@@ -42117,7 +42120,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>46101</v>
       </c>
@@ -42159,7 +42162,7 @@
         <v>1974.08</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>46101</v>
       </c>
@@ -42201,7 +42204,7 @@
         <v>686.76</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>46101</v>
       </c>
@@ -42245,7 +42248,7 @@
         <v>1266.3</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>46102</v>
       </c>
@@ -42289,7 +42292,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>46102</v>
       </c>
@@ -42335,7 +42338,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>46102</v>
       </c>
@@ -42381,7 +42384,7 @@
         <v>112.51</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>46102</v>
       </c>
@@ -42427,7 +42430,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>46103</v>
       </c>
@@ -42469,7 +42472,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>46103</v>
       </c>
@@ -42511,7 +42514,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>46104</v>
       </c>
@@ -42553,7 +42556,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>46104</v>
       </c>
@@ -42597,7 +42600,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>46104</v>
       </c>
@@ -42641,7 +42644,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>46105</v>
       </c>
@@ -42683,7 +42686,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>46105</v>
       </c>
@@ -42729,7 +42732,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>46105</v>
       </c>
@@ -42775,7 +42778,7 @@
         <v>343.38</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>46105</v>
       </c>
@@ -42819,7 +42822,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>46105</v>
       </c>
@@ -42863,7 +42866,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>46105</v>
       </c>
@@ -42907,7 +42910,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>46105</v>
       </c>
@@ -42949,7 +42952,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>46106</v>
       </c>
@@ -42995,7 +42998,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>46106</v>
       </c>
@@ -43039,7 +43042,7 @@
         <v>515.07000000000005</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>46106</v>
       </c>
@@ -43081,7 +43084,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>46106</v>
       </c>
@@ -43127,7 +43130,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>46107</v>
       </c>
@@ -43169,7 +43172,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>46107</v>
       </c>
@@ -43211,7 +43214,7 @@
         <v>5329.92</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>46107</v>
       </c>
@@ -43257,7 +43260,7 @@
         <v>171.69</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>46107</v>
       </c>
@@ -43299,7 +43302,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>46107</v>
       </c>
@@ -43341,7 +43344,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>46108</v>
       </c>
@@ -43383,7 +43386,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>46108</v>
       </c>
@@ -43427,7 +43430,7 @@
         <v>887.5</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>46108</v>
       </c>
@@ -43469,7 +43472,7 @@
         <v>526.55999999999995</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>46108</v>
       </c>
@@ -43515,7 +43518,7 @@
         <v>351.04</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>46108</v>
       </c>
@@ -43559,7 +43562,7 @@
         <v>588.34</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>46109</v>
       </c>
@@ -43603,7 +43606,7 @@
         <v>542.97</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>46109</v>
       </c>
@@ -43645,7 +43648,7 @@
         <v>7268.46</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>46109</v>
       </c>
@@ -43691,7 +43694,7 @@
         <v>175.52</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>46109</v>
       </c>
@@ -43775,7 +43778,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>46109</v>
       </c>
@@ -43819,7 +43822,7 @@
         <v>880.01</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>46110</v>
       </c>
@@ -43861,7 +43864,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>46110</v>
       </c>
@@ -43905,7 +43908,7 @@
         <v>588.34</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>46110</v>
       </c>
@@ -43949,7 +43952,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>46111</v>
       </c>
@@ -43993,7 +43996,7 @@
         <v>882.51</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>46111</v>
       </c>
@@ -44039,7 +44042,7 @@
         <v>175.52</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>46111</v>
       </c>
@@ -44085,7 +44088,7 @@
         <v>1916.64</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>46112</v>
       </c>
@@ -44127,7 +44130,7 @@
         <v>8842.2999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>46112</v>
       </c>
@@ -44169,7 +44172,7 @@
         <v>50923</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>46112</v>
       </c>
@@ -44215,7 +44218,7 @@
         <v>175.52</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>46112</v>
       </c>
@@ -44261,7 +44264,7 @@
         <v>175.52</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>46112</v>
       </c>
@@ -44307,7 +44310,7 @@
         <v>175.52</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>46112</v>
       </c>
@@ -44353,7 +44356,8 @@
         <v>175.52</v>
       </c>
     </row>
-    <row r="178" spans="12:16" x14ac:dyDescent="0.3">
+    <row r="177" spans="12:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="178" spans="12:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="L178">
         <f>SUM(L2:L176)</f>
         <v>156624.39428571428</v>
@@ -44368,12 +44372,20 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="G1:G178" xr:uid="{60ED403F-78CB-6D47-BB80-6E9874AF083C}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SHIPPINGFEE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DA079A-99A1-6646-8B96-5038ACA25398}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X188"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -44454,7 +44466,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>46054</v>
       </c>
@@ -44496,7 +44508,7 @@
         <v>1809.9</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>46054</v>
       </c>
@@ -44538,7 +44550,7 @@
         <v>341.44</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>46055</v>
       </c>
@@ -44578,7 +44590,7 @@
         <v>147.66</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>46055</v>
       </c>
@@ -44620,7 +44632,7 @@
         <v>134.1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46055</v>
       </c>
@@ -44660,7 +44672,7 @@
         <v>134.1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>46055</v>
       </c>
@@ -44702,7 +44714,7 @@
         <v>147.66</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>46055</v>
       </c>
@@ -44744,7 +44756,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>46055</v>
       </c>
@@ -44786,7 +44798,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>46055</v>
       </c>
@@ -44828,7 +44840,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>46055</v>
       </c>
@@ -44868,7 +44880,7 @@
         <v>343.27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>46055</v>
       </c>
@@ -44910,7 +44922,7 @@
         <v>4057.96</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>46055</v>
       </c>
@@ -44952,7 +44964,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>46055</v>
       </c>
@@ -44994,7 +45006,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46055</v>
       </c>
@@ -45036,7 +45048,7 @@
         <v>713.29</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>46056</v>
       </c>
@@ -45076,7 +45088,7 @@
         <v>514.89</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>46056</v>
       </c>
@@ -45116,7 +45128,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46056</v>
       </c>
@@ -45158,7 +45170,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46056</v>
       </c>
@@ -45200,7 +45212,7 @@
         <v>532.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>46057</v>
       </c>
@@ -45240,7 +45252,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>46057</v>
       </c>
@@ -45280,7 +45292,7 @@
         <v>686.52</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>46057</v>
       </c>
@@ -45324,7 +45336,7 @@
         <v>33757.589999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46057</v>
       </c>
@@ -45366,7 +45378,7 @@
         <v>640.47</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46057</v>
       </c>
@@ -45408,7 +45420,7 @@
         <v>584.70000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>46057</v>
       </c>
@@ -45450,7 +45462,7 @@
         <v>1387.14</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46057</v>
       </c>
@@ -45492,7 +45504,7 @@
         <v>2556.8200000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46057</v>
       </c>
@@ -45534,7 +45546,7 @@
         <v>1085.94</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46057</v>
       </c>
@@ -45576,7 +45588,7 @@
         <v>1469.94</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>46057</v>
       </c>
@@ -45618,7 +45630,7 @@
         <v>396.84</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>46057</v>
       </c>
@@ -45660,7 +45672,7 @@
         <v>931.28</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>46057</v>
       </c>
@@ -45742,7 +45754,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46058</v>
       </c>
@@ -45784,7 +45796,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>46058</v>
       </c>
@@ -45826,7 +45838,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46058</v>
       </c>
@@ -45866,7 +45878,7 @@
         <v>11842.3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46058</v>
       </c>
@@ -45906,7 +45918,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46058</v>
       </c>
@@ -45948,7 +45960,7 @@
         <v>861.28</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46058</v>
       </c>
@@ -45988,7 +46000,7 @@
         <v>15184.6</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46058</v>
       </c>
@@ -46028,7 +46040,7 @@
         <v>5073.84</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>46058</v>
       </c>
@@ -46070,7 +46082,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>46058</v>
       </c>
@@ -46112,7 +46124,7 @@
         <v>4220</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>46058</v>
       </c>
@@ -46154,7 +46166,7 @@
         <v>533.34</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>46058</v>
       </c>
@@ -46194,7 +46206,7 @@
         <v>6342.3</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>46058</v>
       </c>
@@ -46236,7 +46248,7 @@
         <v>6378.58</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>46059</v>
       </c>
@@ -46276,7 +46288,7 @@
         <v>30369.200000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>46059</v>
       </c>
@@ -46318,7 +46330,7 @@
         <v>588.34</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46059</v>
       </c>
@@ -46358,7 +46370,7 @@
         <v>1844.2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46059</v>
       </c>
@@ -46398,7 +46410,7 @@
         <v>5916.81</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46059</v>
       </c>
@@ -46440,7 +46452,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46059</v>
       </c>
@@ -46480,7 +46492,7 @@
         <v>2018.46</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46059</v>
       </c>
@@ -46524,7 +46536,7 @@
         <v>101272.77</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>46060</v>
       </c>
@@ -46566,7 +46578,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>46060</v>
       </c>
@@ -46606,7 +46618,7 @@
         <v>343.26</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>46060</v>
       </c>
@@ -46646,7 +46658,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>46060</v>
       </c>
@@ -46688,7 +46700,7 @@
         <v>224.96</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>46061</v>
       </c>
@@ -46728,7 +46740,7 @@
         <v>713.29</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>46061</v>
       </c>
@@ -46768,7 +46780,7 @@
         <v>1076.5999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>46061</v>
       </c>
@@ -46808,7 +46820,7 @@
         <v>887.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>46061</v>
       </c>
@@ -46850,7 +46862,7 @@
         <v>887.14</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>46062</v>
       </c>
@@ -46892,7 +46904,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>46062</v>
       </c>
@@ -46934,7 +46946,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>46063</v>
       </c>
@@ -46974,7 +46986,7 @@
         <v>514.9</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>46063</v>
       </c>
@@ -47016,7 +47028,7 @@
         <v>320.24</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>46063</v>
       </c>
@@ -47058,7 +47070,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>46063</v>
       </c>
@@ -47098,7 +47110,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>46063</v>
       </c>
@@ -47140,7 +47152,7 @@
         <v>3329.7</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>46063</v>
       </c>
@@ -47182,7 +47194,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>46063</v>
       </c>
@@ -47224,7 +47236,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>46063</v>
       </c>
@@ -47266,7 +47278,7 @@
         <v>6400.1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>46064</v>
       </c>
@@ -47308,7 +47320,7 @@
         <v>260.8</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>46064</v>
       </c>
@@ -47350,7 +47362,7 @@
         <v>260.8</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>46064</v>
       </c>
@@ -47390,7 +47402,7 @@
         <v>343.27</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>46064</v>
       </c>
@@ -47432,7 +47444,7 @@
         <v>521.6</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>46064</v>
       </c>
@@ -47474,7 +47486,7 @@
         <v>142.72</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>46064</v>
       </c>
@@ -47514,7 +47526,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>46064</v>
       </c>
@@ -47556,7 +47568,7 @@
         <v>3185.52</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>46065</v>
       </c>
@@ -47598,7 +47610,7 @@
         <v>844.32</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>46065</v>
       </c>
@@ -47642,7 +47654,7 @@
         <v>468.36</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>46065</v>
       </c>
@@ -47726,7 +47738,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>46066</v>
       </c>
@@ -47768,7 +47780,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>46066</v>
       </c>
@@ -47808,7 +47820,7 @@
         <v>514.9</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>46066</v>
       </c>
@@ -47850,7 +47862,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>46066</v>
       </c>
@@ -47890,7 +47902,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>46066</v>
       </c>
@@ -47930,7 +47942,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>46066</v>
       </c>
@@ -47970,7 +47982,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>46066</v>
       </c>
@@ -48012,7 +48024,7 @@
         <v>1176.68</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>46066</v>
       </c>
@@ -48054,7 +48066,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>46066</v>
       </c>
@@ -48094,7 +48106,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>46067</v>
       </c>
@@ -48132,7 +48144,7 @@
         <v>3584.54</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>46067</v>
       </c>
@@ -48172,7 +48184,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>46068</v>
       </c>
@@ -48212,7 +48224,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>46068</v>
       </c>
@@ -48252,7 +48264,7 @@
         <v>514.9</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>46068</v>
       </c>
@@ -48294,7 +48306,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>46068</v>
       </c>
@@ -48334,7 +48346,7 @@
         <v>1972.16</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>46068</v>
       </c>
@@ -48376,7 +48388,7 @@
         <v>-78.400000000000006</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>46069</v>
       </c>
@@ -48456,7 +48468,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>46069</v>
       </c>
@@ -48494,7 +48506,7 @@
         <v>3584.54</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>46069</v>
       </c>
@@ -48536,7 +48548,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>46069</v>
       </c>
@@ -48576,7 +48588,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>46069</v>
       </c>
@@ -48618,7 +48630,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>46069</v>
       </c>
@@ -48660,7 +48672,7 @@
         <v>861.28</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>46070</v>
       </c>
@@ -48700,7 +48712,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>46070</v>
       </c>
@@ -48740,7 +48752,7 @@
         <v>1716.3</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>46070</v>
       </c>
@@ -48782,7 +48794,7 @@
         <v>673.02</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>46070</v>
       </c>
@@ -48822,7 +48834,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>46070</v>
       </c>
@@ -48864,7 +48876,7 @@
         <v>588.34</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>46070</v>
       </c>
@@ -48906,7 +48918,7 @@
         <v>336.1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>46071</v>
       </c>
@@ -48946,7 +48958,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>46071</v>
       </c>
@@ -48988,7 +49000,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>46071</v>
       </c>
@@ -49028,7 +49040,7 @@
         <v>686.52</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>46071</v>
       </c>
@@ -49068,7 +49080,7 @@
         <v>44053.8</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>46071</v>
       </c>
@@ -49110,7 +49122,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>46072</v>
       </c>
@@ -49152,7 +49164,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>46072</v>
       </c>
@@ -49192,7 +49204,7 @@
         <v>514.89</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>46072</v>
       </c>
@@ -49234,7 +49246,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>46073</v>
       </c>
@@ -49276,7 +49288,7 @@
         <v>532.5</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>46073</v>
       </c>
@@ -49316,7 +49328,7 @@
         <v>55923</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>46073</v>
       </c>
@@ -49356,7 +49368,7 @@
         <v>13321.6</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>46073</v>
       </c>
@@ -49398,7 +49410,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>46073</v>
       </c>
@@ -49440,7 +49452,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>46073</v>
       </c>
@@ -49482,7 +49494,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>46073</v>
       </c>
@@ -49522,7 +49534,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>46073</v>
       </c>
@@ -49562,7 +49574,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>46073</v>
       </c>
@@ -49604,7 +49616,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>46073</v>
       </c>
@@ -49646,7 +49658,7 @@
         <v>466.45</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>46074</v>
       </c>
@@ -49686,7 +49698,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>46074</v>
       </c>
@@ -49726,7 +49738,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>46074</v>
       </c>
@@ -49766,7 +49778,7 @@
         <v>343.27</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>46074</v>
       </c>
@@ -49804,7 +49816,7 @@
         <v>1768.46</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>46075</v>
       </c>
@@ -49846,7 +49858,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>46075</v>
       </c>
@@ -49886,7 +49898,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>46075</v>
       </c>
@@ -49926,7 +49938,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>46075</v>
       </c>
@@ -49968,7 +49980,7 @@
         <v>142.72</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>46075</v>
       </c>
@@ -50008,7 +50020,7 @@
         <v>858.15</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>46075</v>
       </c>
@@ -50050,7 +50062,7 @@
         <v>521.6</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>46075</v>
       </c>
@@ -50090,7 +50102,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>46075</v>
       </c>
@@ -50132,7 +50144,7 @@
         <v>449.92</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>46075</v>
       </c>
@@ -50174,7 +50186,7 @@
         <v>336.1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>46076</v>
       </c>
@@ -50216,7 +50228,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>46076</v>
       </c>
@@ -50256,7 +50268,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>46076</v>
       </c>
@@ -50296,7 +50308,7 @@
         <v>343.26</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>46076</v>
       </c>
@@ -50338,7 +50350,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>46076</v>
       </c>
@@ -50378,7 +50390,7 @@
         <v>858.15</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>46076</v>
       </c>
@@ -50418,7 +50430,7 @@
         <v>1468.46</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>46078</v>
       </c>
@@ -50458,7 +50470,7 @@
         <v>2018.46</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>46078</v>
       </c>
@@ -50496,7 +50508,7 @@
         <v>3584.54</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>46078</v>
       </c>
@@ -50536,7 +50548,7 @@
         <v>887.5</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>46078</v>
       </c>
@@ -50574,7 +50586,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>46078</v>
       </c>
@@ -50614,7 +50626,7 @@
         <v>343.26</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>46078</v>
       </c>
@@ -50654,7 +50666,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>46078</v>
       </c>
@@ -50696,7 +50708,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>46078</v>
       </c>
@@ -50738,7 +50750,7 @@
         <v>1176.68</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>46078</v>
       </c>
@@ -50778,7 +50790,7 @@
         <v>147.78</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>46078</v>
       </c>
@@ -50818,7 +50830,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>46078</v>
       </c>
@@ -50858,7 +50870,7 @@
         <v>430.64</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>46078</v>
       </c>
@@ -50898,7 +50910,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>46078</v>
       </c>
@@ -50938,7 +50950,7 @@
         <v>2444.1999999999998</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>46078</v>
       </c>
@@ -50980,7 +50992,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>46078</v>
       </c>
@@ -51022,7 +51034,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>46078</v>
       </c>
@@ -51062,7 +51074,7 @@
         <v>858.15</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>46078</v>
       </c>
@@ -51102,7 +51114,7 @@
         <v>1518.46</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>46078</v>
       </c>
@@ -51144,7 +51156,7 @@
         <v>180.99</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>46078</v>
       </c>
@@ -51186,7 +51198,7 @@
         <v>341.44</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>46078</v>
       </c>
@@ -51230,7 +51242,7 @@
         <v>156.12</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>46079</v>
       </c>
@@ -51272,7 +51284,7 @@
         <v>13057.69</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>46079</v>
       </c>
@@ -51312,7 +51324,7 @@
         <v>171.63</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>46079</v>
       </c>
@@ -51354,7 +51366,7 @@
         <v>882.51</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>46079</v>
       </c>
@@ -51396,7 +51408,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>46080</v>
       </c>
@@ -51436,7 +51448,7 @@
         <v>7073.84</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>46080</v>
       </c>
@@ -51478,7 +51490,7 @@
         <v>1076.5999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>46080</v>
       </c>
@@ -51520,7 +51532,7 @@
         <v>713.29</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>46080</v>
       </c>
@@ -51562,7 +51574,7 @@
         <v>168.05</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>46080</v>
       </c>
@@ -51642,7 +51654,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>46080</v>
       </c>
@@ -51682,7 +51694,7 @@
         <v>514.89</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>46080</v>
       </c>
@@ -51724,7 +51736,7 @@
         <v>215.32</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>46080</v>
       </c>
@@ -51766,7 +51778,7 @@
         <v>542.97</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>46080</v>
       </c>
@@ -51808,7 +51820,7 @@
         <v>168.05</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>46080</v>
       </c>
@@ -51848,7 +51860,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>46081</v>
       </c>
@@ -51888,7 +51900,7 @@
         <v>2368.46</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>46081</v>
       </c>
@@ -51930,7 +51942,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>46081</v>
       </c>
@@ -51972,7 +51984,7 @@
         <v>1176.68</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>46081</v>
       </c>
@@ -52014,7 +52026,7 @@
         <v>294.17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>46081</v>
       </c>
@@ -52056,7 +52068,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L187" t="s">
         <v>1062</v>
       </c>
@@ -52067,7 +52079,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L188">
         <f>SUM(L2:L186)</f>
         <v>449008.19757139985</v>
@@ -52082,12 +52094,20 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="G1:G188" xr:uid="{21DA079A-99A1-6646-8B96-5038ACA25398}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SHIPPINGFEE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227A76A5-0D02-6F47-A831-12FB6501A393}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA187"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -52168,7 +52188,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>46023</v>
       </c>
@@ -52227,7 +52247,7 @@
       <c r="Z2" s="10"/>
       <c r="AA2" s="10"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>46023</v>
       </c>
@@ -52288,7 +52308,7 @@
       <c r="Z3" s="10"/>
       <c r="AA3" s="10"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>46024</v>
       </c>
@@ -52351,7 +52371,7 @@
       <c r="Z4" s="10"/>
       <c r="AA4" s="10"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>46024</v>
       </c>
@@ -52414,7 +52434,7 @@
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46024</v>
       </c>
@@ -52471,7 +52491,7 @@
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>46024</v>
       </c>
@@ -52532,7 +52552,7 @@
       <c r="Z7" s="10"/>
       <c r="AA7" s="10"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>46024</v>
       </c>
@@ -52593,7 +52613,7 @@
       <c r="Z8" s="10"/>
       <c r="AA8" s="10"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>46024</v>
       </c>
@@ -52650,7 +52670,7 @@
       <c r="Z9" s="10"/>
       <c r="AA9" s="10"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>46025</v>
       </c>
@@ -52711,7 +52731,7 @@
       <c r="Z10" s="10"/>
       <c r="AA10" s="10"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>46025</v>
       </c>
@@ -52772,7 +52792,7 @@
       <c r="Z11" s="10"/>
       <c r="AA11" s="10"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>46025</v>
       </c>
@@ -52835,7 +52855,7 @@
       <c r="Z12" s="10"/>
       <c r="AA12" s="10"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>46025</v>
       </c>
@@ -52898,7 +52918,7 @@
       <c r="Z13" s="10"/>
       <c r="AA13" s="10"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>46025</v>
       </c>
@@ -52959,7 +52979,7 @@
       <c r="Z14" s="10"/>
       <c r="AA14" s="10"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46025</v>
       </c>
@@ -53012,7 +53032,7 @@
       <c r="Z15" s="10"/>
       <c r="AA15" s="10"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>46026</v>
       </c>
@@ -53073,7 +53093,7 @@
       <c r="Z16" s="10"/>
       <c r="AA16" s="10"/>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>46026</v>
       </c>
@@ -53134,7 +53154,7 @@
       <c r="Z17" s="10"/>
       <c r="AA17" s="10"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46026</v>
       </c>
@@ -53197,7 +53217,7 @@
       <c r="Z18" s="10"/>
       <c r="AA18" s="10"/>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46026</v>
       </c>
@@ -53258,7 +53278,7 @@
       <c r="Z19" s="10"/>
       <c r="AA19" s="10"/>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>46027</v>
       </c>
@@ -53321,7 +53341,7 @@
       <c r="Z20" s="10"/>
       <c r="AA20" s="10"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>46027</v>
       </c>
@@ -53382,7 +53402,7 @@
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>46027</v>
       </c>
@@ -53439,7 +53459,7 @@
       <c r="Z22" s="10"/>
       <c r="AA22" s="10"/>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46027</v>
       </c>
@@ -53498,7 +53518,7 @@
       <c r="Z23" s="10"/>
       <c r="AA23" s="10"/>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46027</v>
       </c>
@@ -53559,7 +53579,7 @@
       <c r="Z24" s="10"/>
       <c r="AA24" s="10"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>46027</v>
       </c>
@@ -53616,7 +53636,7 @@
       <c r="Z25" s="10"/>
       <c r="AA25" s="10"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46027</v>
       </c>
@@ -53673,7 +53693,7 @@
       <c r="Z26" s="10"/>
       <c r="AA26" s="10"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46027</v>
       </c>
@@ -53732,7 +53752,7 @@
       <c r="Z27" s="10"/>
       <c r="AA27" s="10"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46027</v>
       </c>
@@ -53791,7 +53811,7 @@
       <c r="Z28" s="10"/>
       <c r="AA28" s="10"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>46027</v>
       </c>
@@ -53850,7 +53870,7 @@
       <c r="Z29" s="10"/>
       <c r="AA29" s="10"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>46028</v>
       </c>
@@ -53913,7 +53933,7 @@
       <c r="Z30" s="10"/>
       <c r="AA30" s="10"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>46028</v>
       </c>
@@ -53974,7 +53994,7 @@
       <c r="Z31" s="10"/>
       <c r="AA31" s="10"/>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>46028</v>
       </c>
@@ -54035,7 +54055,7 @@
       <c r="Z32" s="10"/>
       <c r="AA32" s="10"/>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46028</v>
       </c>
@@ -54096,7 +54116,7 @@
       <c r="Z33" s="10"/>
       <c r="AA33" s="10"/>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>46028</v>
       </c>
@@ -54157,7 +54177,7 @@
       <c r="Z34" s="10"/>
       <c r="AA34" s="10"/>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46028</v>
       </c>
@@ -54218,7 +54238,7 @@
       <c r="Z35" s="10"/>
       <c r="AA35" s="10"/>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46028</v>
       </c>
@@ -54281,7 +54301,7 @@
       <c r="Z36" s="10"/>
       <c r="AA36" s="10"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46028</v>
       </c>
@@ -54342,7 +54362,7 @@
       <c r="Z37" s="10"/>
       <c r="AA37" s="10"/>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46028</v>
       </c>
@@ -54403,7 +54423,7 @@
       <c r="Z38" s="10"/>
       <c r="AA38" s="10"/>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46028</v>
       </c>
@@ -54460,7 +54480,7 @@
       <c r="Z39" s="10"/>
       <c r="AA39" s="10"/>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>46028</v>
       </c>
@@ -54519,7 +54539,7 @@
       <c r="Z40" s="10"/>
       <c r="AA40" s="10"/>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>46028</v>
       </c>
@@ -54578,7 +54598,7 @@
       <c r="Z41" s="10"/>
       <c r="AA41" s="10"/>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>46028</v>
       </c>
@@ -54637,7 +54657,7 @@
       <c r="Z42" s="10"/>
       <c r="AA42" s="10"/>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>46028</v>
       </c>
@@ -54753,7 +54773,7 @@
       <c r="Z44" s="10"/>
       <c r="AA44" s="10"/>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>46029</v>
       </c>
@@ -54814,7 +54834,7 @@
       <c r="Z45" s="10"/>
       <c r="AA45" s="10"/>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>46029</v>
       </c>
@@ -54932,7 +54952,7 @@
       <c r="Z47" s="10"/>
       <c r="AA47" s="10"/>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46029</v>
       </c>
@@ -54995,7 +55015,7 @@
       <c r="Z48" s="10"/>
       <c r="AA48" s="10"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46029</v>
       </c>
@@ -55056,7 +55076,7 @@
       <c r="Z49" s="10"/>
       <c r="AA49" s="10"/>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46029</v>
       </c>
@@ -55117,7 +55137,7 @@
       <c r="Z50" s="10"/>
       <c r="AA50" s="10"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46029</v>
       </c>
@@ -55174,7 +55194,7 @@
       <c r="Z51" s="10"/>
       <c r="AA51" s="10"/>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>46029</v>
       </c>
@@ -55235,7 +55255,7 @@
       <c r="Z52" s="10"/>
       <c r="AA52" s="10"/>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>46029</v>
       </c>
@@ -55296,7 +55316,7 @@
       <c r="Z53" s="10"/>
       <c r="AA53" s="10"/>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>46029</v>
       </c>
@@ -55353,7 +55373,7 @@
       <c r="Z54" s="10"/>
       <c r="AA54" s="10"/>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>46029</v>
       </c>
@@ -55410,7 +55430,7 @@
       <c r="Z55" s="10"/>
       <c r="AA55" s="10"/>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>46029</v>
       </c>
@@ -55473,7 +55493,7 @@
       <c r="Z56" s="10"/>
       <c r="AA56" s="10"/>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>46029</v>
       </c>
@@ -55534,7 +55554,7 @@
       <c r="Z57" s="10"/>
       <c r="AA57" s="10"/>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>46029</v>
       </c>
@@ -55593,7 +55613,7 @@
       <c r="Z58" s="10"/>
       <c r="AA58" s="10"/>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>46029</v>
       </c>
@@ -55652,7 +55672,7 @@
       <c r="Z59" s="10"/>
       <c r="AA59" s="10"/>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>46029</v>
       </c>
@@ -55711,7 +55731,7 @@
       <c r="Z60" s="10"/>
       <c r="AA60" s="10"/>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>46030</v>
       </c>
@@ -55768,7 +55788,7 @@
       <c r="Z61" s="10"/>
       <c r="AA61" s="10"/>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>46030</v>
       </c>
@@ -55823,7 +55843,7 @@
       <c r="Z62" s="10"/>
       <c r="AA62" s="10"/>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>46030</v>
       </c>
@@ -55878,7 +55898,7 @@
       <c r="Z63" s="10"/>
       <c r="AA63" s="10"/>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>46030</v>
       </c>
@@ -55933,7 +55953,7 @@
       <c r="Z64" s="10"/>
       <c r="AA64" s="10"/>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>46030</v>
       </c>
@@ -55994,7 +56014,7 @@
       <c r="Z65" s="10"/>
       <c r="AA65" s="10"/>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>46031</v>
       </c>
@@ -56053,7 +56073,7 @@
       <c r="Z66" s="10"/>
       <c r="AA66" s="10"/>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>46031</v>
       </c>
@@ -56116,7 +56136,7 @@
       <c r="Z67" s="10"/>
       <c r="AA67" s="10"/>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>46031</v>
       </c>
@@ -56177,7 +56197,7 @@
       <c r="Z68" s="10"/>
       <c r="AA68" s="10"/>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>46032</v>
       </c>
@@ -56240,7 +56260,7 @@
       <c r="Z69" s="10"/>
       <c r="AA69" s="10"/>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>46032</v>
       </c>
@@ -56301,7 +56321,7 @@
       <c r="Z70" s="10"/>
       <c r="AA70" s="10"/>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>46032</v>
       </c>
@@ -56364,7 +56384,7 @@
       <c r="Z71" s="10"/>
       <c r="AA71" s="10"/>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>46032</v>
       </c>
@@ -56419,7 +56439,7 @@
       <c r="Z72" s="10"/>
       <c r="AA72" s="10"/>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>46034</v>
       </c>
@@ -56470,7 +56490,7 @@
       <c r="Z73" s="10"/>
       <c r="AA73" s="10"/>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>46034</v>
       </c>
@@ -56531,7 +56551,7 @@
       <c r="Z74" s="10"/>
       <c r="AA74" s="10"/>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>46034</v>
       </c>
@@ -56592,7 +56612,7 @@
       <c r="Z75" s="10"/>
       <c r="AA75" s="10"/>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>46034</v>
       </c>
@@ -56655,7 +56675,7 @@
       <c r="Z76" s="10"/>
       <c r="AA76" s="10"/>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>46034</v>
       </c>
@@ -56716,7 +56736,7 @@
       <c r="Z77" s="10"/>
       <c r="AA77" s="10"/>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>46034</v>
       </c>
@@ -56777,7 +56797,7 @@
       <c r="Z78" s="10"/>
       <c r="AA78" s="10"/>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>46034</v>
       </c>
@@ -56838,7 +56858,7 @@
       <c r="Z79" s="10"/>
       <c r="AA79" s="10"/>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>46034</v>
       </c>
@@ -56901,7 +56921,7 @@
       <c r="Z80" s="10"/>
       <c r="AA80" s="10"/>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>46034</v>
       </c>
@@ -56964,7 +56984,7 @@
       <c r="Z81" s="10"/>
       <c r="AA81" s="10"/>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>46034</v>
       </c>
@@ -57025,7 +57045,7 @@
       <c r="Z82" s="10"/>
       <c r="AA82" s="10"/>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>46034</v>
       </c>
@@ -57139,7 +57159,7 @@
       <c r="Z84" s="10"/>
       <c r="AA84" s="10"/>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>46034</v>
       </c>
@@ -57200,7 +57220,7 @@
       <c r="Z85" s="10"/>
       <c r="AA85" s="10"/>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>46034</v>
       </c>
@@ -57263,7 +57283,7 @@
       <c r="Z86" s="10"/>
       <c r="AA86" s="10"/>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>46035</v>
       </c>
@@ -57324,7 +57344,7 @@
       <c r="Z87" s="10"/>
       <c r="AA87" s="10"/>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>46035</v>
       </c>
@@ -57379,7 +57399,7 @@
       <c r="Z88" s="10"/>
       <c r="AA88" s="10"/>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>46035</v>
       </c>
@@ -57438,7 +57458,7 @@
       <c r="Z89" s="10"/>
       <c r="AA89" s="10"/>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>46035</v>
       </c>
@@ -57493,7 +57513,7 @@
       <c r="Z90" s="10"/>
       <c r="AA90" s="10"/>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>46036</v>
       </c>
@@ -57550,7 +57570,7 @@
       <c r="Z91" s="10"/>
       <c r="AA91" s="10"/>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>46036</v>
       </c>
@@ -57609,7 +57629,7 @@
       <c r="Z92" s="10"/>
       <c r="AA92" s="10"/>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>46036</v>
       </c>
@@ -57668,7 +57688,7 @@
       <c r="Z93" s="10"/>
       <c r="AA93" s="10"/>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>46036</v>
       </c>
@@ -57725,7 +57745,7 @@
       <c r="Z94" s="10"/>
       <c r="AA94" s="10"/>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>46036</v>
       </c>
@@ -57786,7 +57806,7 @@
       <c r="Z95" s="10"/>
       <c r="AA95" s="10"/>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>46036</v>
       </c>
@@ -57847,7 +57867,7 @@
       <c r="Z96" s="10"/>
       <c r="AA96" s="10"/>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>46036</v>
       </c>
@@ -57908,7 +57928,7 @@
       <c r="Z97" s="10"/>
       <c r="AA97" s="10"/>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>46036</v>
       </c>
@@ -57965,7 +57985,7 @@
       <c r="Z98" s="10"/>
       <c r="AA98" s="10"/>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>46037</v>
       </c>
@@ -58020,7 +58040,7 @@
       <c r="Z99" s="10"/>
       <c r="AA99" s="10"/>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>46037</v>
       </c>
@@ -58081,7 +58101,7 @@
       <c r="Z100" s="10"/>
       <c r="AA100" s="10"/>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>46037</v>
       </c>
@@ -58142,7 +58162,7 @@
       <c r="Z101" s="10"/>
       <c r="AA101" s="10"/>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>46037</v>
       </c>
@@ -58203,7 +58223,7 @@
       <c r="Z102" s="10"/>
       <c r="AA102" s="10"/>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>46037</v>
       </c>
@@ -58266,7 +58286,7 @@
       <c r="Z103" s="10"/>
       <c r="AA103" s="10"/>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>46037</v>
       </c>
@@ -58384,7 +58404,7 @@
       <c r="Z105" s="10"/>
       <c r="AA105" s="10"/>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>46037</v>
       </c>
@@ -58445,7 +58465,7 @@
       <c r="Z106" s="10"/>
       <c r="AA106" s="10"/>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>46038</v>
       </c>
@@ -58508,7 +58528,7 @@
       <c r="Z107" s="10"/>
       <c r="AA107" s="10"/>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>46038</v>
       </c>
@@ -58563,7 +58583,7 @@
       <c r="Z108" s="10"/>
       <c r="AA108" s="10"/>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>46038</v>
       </c>
@@ -58622,7 +58642,7 @@
       <c r="Z109" s="10"/>
       <c r="AA109" s="10"/>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>46039</v>
       </c>
@@ -58683,7 +58703,7 @@
       <c r="Z110" s="10"/>
       <c r="AA110" s="10"/>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>46039</v>
       </c>
@@ -58746,7 +58766,7 @@
       <c r="Z111" s="10"/>
       <c r="AA111" s="10"/>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>46039</v>
       </c>
@@ -58809,7 +58829,7 @@
       <c r="Z112" s="10"/>
       <c r="AA112" s="10"/>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>46039</v>
       </c>
@@ -58870,7 +58890,7 @@
       <c r="Z113" s="10"/>
       <c r="AA113" s="10"/>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>46041</v>
       </c>
@@ -58931,7 +58951,7 @@
       <c r="Z114" s="10"/>
       <c r="AA114" s="10"/>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>46041</v>
       </c>
@@ -58992,7 +59012,7 @@
       <c r="Z115" s="10"/>
       <c r="AA115" s="10"/>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>46041</v>
       </c>
@@ -59053,7 +59073,7 @@
       <c r="Z116" s="10"/>
       <c r="AA116" s="10"/>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>46041</v>
       </c>
@@ -59114,7 +59134,7 @@
       <c r="Z117" s="10"/>
       <c r="AA117" s="10"/>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>46042</v>
       </c>
@@ -59175,7 +59195,7 @@
       <c r="Z118" s="10"/>
       <c r="AA118" s="10"/>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>46042</v>
       </c>
@@ -59236,7 +59256,7 @@
       <c r="Z119" s="10"/>
       <c r="AA119" s="10"/>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>46042</v>
       </c>
@@ -59299,7 +59319,7 @@
       <c r="Z120" s="10"/>
       <c r="AA120" s="10"/>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>46042</v>
       </c>
@@ -59360,7 +59380,7 @@
       <c r="Z121" s="10"/>
       <c r="AA121" s="10"/>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>46042</v>
       </c>
@@ -59423,7 +59443,7 @@
       <c r="Z122" s="10"/>
       <c r="AA122" s="10"/>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>46042</v>
       </c>
@@ -59484,7 +59504,7 @@
       <c r="Z123" s="10"/>
       <c r="AA123" s="10"/>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>46043</v>
       </c>
@@ -59545,7 +59565,7 @@
       <c r="Z124" s="10"/>
       <c r="AA124" s="10"/>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>46043</v>
       </c>
@@ -59663,7 +59683,7 @@
       <c r="Z126" s="10"/>
       <c r="AA126" s="10"/>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>46043</v>
       </c>
@@ -59726,7 +59746,7 @@
       <c r="Z127" s="10"/>
       <c r="AA127" s="10"/>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>46044</v>
       </c>
@@ -59781,7 +59801,7 @@
       <c r="Z128" s="10"/>
       <c r="AA128" s="10"/>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>46044</v>
       </c>
@@ -59842,7 +59862,7 @@
       <c r="Z129" s="10"/>
       <c r="AA129" s="10"/>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>46044</v>
       </c>
@@ -59903,7 +59923,7 @@
       <c r="Z130" s="10"/>
       <c r="AA130" s="10"/>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>46044</v>
       </c>
@@ -59964,7 +59984,7 @@
       <c r="Z131" s="10"/>
       <c r="AA131" s="10"/>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>46045</v>
       </c>
@@ -60027,7 +60047,7 @@
       <c r="Z132" s="10"/>
       <c r="AA132" s="10"/>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>46045</v>
       </c>
@@ -60090,7 +60110,7 @@
       <c r="Z133" s="10"/>
       <c r="AA133" s="10"/>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>46045</v>
       </c>
@@ -60153,7 +60173,7 @@
       <c r="Z134" s="10"/>
       <c r="AA134" s="10"/>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>46045</v>
       </c>
@@ -60216,7 +60236,7 @@
       <c r="Z135" s="10"/>
       <c r="AA135" s="10"/>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>46045</v>
       </c>
@@ -60275,7 +60295,7 @@
       <c r="Z136" s="10"/>
       <c r="AA136" s="10"/>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>46046</v>
       </c>
@@ -60338,7 +60358,7 @@
       <c r="Z137" s="10"/>
       <c r="AA137" s="10"/>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>46046</v>
       </c>
@@ -60401,7 +60421,7 @@
       <c r="Z138" s="10"/>
       <c r="AA138" s="10"/>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>46048</v>
       </c>
@@ -60464,7 +60484,7 @@
       <c r="Z139" s="10"/>
       <c r="AA139" s="10"/>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>46048</v>
       </c>
@@ -60527,7 +60547,7 @@
       <c r="Z140" s="10"/>
       <c r="AA140" s="10"/>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>46048</v>
       </c>
@@ -60590,7 +60610,7 @@
       <c r="Z141" s="10"/>
       <c r="AA141" s="10"/>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>46048</v>
       </c>
@@ -60653,7 +60673,7 @@
       <c r="Z142" s="10"/>
       <c r="AA142" s="10"/>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>46048</v>
       </c>
@@ -60718,7 +60738,7 @@
       <c r="Z143" s="10"/>
       <c r="AA143" s="10"/>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>46048</v>
       </c>
@@ -60785,7 +60805,7 @@
       <c r="Z144" s="10"/>
       <c r="AA144" s="10"/>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>46048</v>
       </c>
@@ -60844,7 +60864,7 @@
       <c r="Z145" s="10"/>
       <c r="AA145" s="10"/>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>46049</v>
       </c>
@@ -60905,7 +60925,7 @@
       <c r="Z146" s="10"/>
       <c r="AA146" s="10"/>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>46049</v>
       </c>
@@ -60962,7 +60982,7 @@
       <c r="Z147" s="10"/>
       <c r="AA147" s="10"/>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>46051</v>
       </c>
@@ -61025,7 +61045,7 @@
       <c r="Z148" s="10"/>
       <c r="AA148" s="10"/>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>46051</v>
       </c>
@@ -61086,7 +61106,7 @@
       <c r="Z149" s="10"/>
       <c r="AA149" s="10"/>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>46051</v>
       </c>
@@ -61149,7 +61169,7 @@
       <c r="Z150" s="10"/>
       <c r="AA150" s="10"/>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>46051</v>
       </c>
@@ -61259,7 +61279,7 @@
       <c r="Z152" s="10"/>
       <c r="AA152" s="10"/>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>46051</v>
       </c>
@@ -61369,7 +61389,7 @@
       <c r="Z154" s="10"/>
       <c r="AA154" s="10"/>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>46051</v>
       </c>
@@ -61479,7 +61499,7 @@
       <c r="Z156" s="10"/>
       <c r="AA156" s="10"/>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>46051</v>
       </c>
@@ -61532,7 +61552,7 @@
       <c r="Z157" s="10"/>
       <c r="AA157" s="10"/>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>46051</v>
       </c>
@@ -61587,7 +61607,7 @@
       <c r="Z158" s="10"/>
       <c r="AA158" s="10"/>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>46051</v>
       </c>
@@ -61644,7 +61664,7 @@
       <c r="Z159" s="10"/>
       <c r="AA159" s="10"/>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>46051</v>
       </c>
@@ -61697,7 +61717,7 @@
       <c r="Z160" s="10"/>
       <c r="AA160" s="10"/>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>46052</v>
       </c>
@@ -61752,7 +61772,7 @@
       <c r="Z161" s="10"/>
       <c r="AA161" s="10"/>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>46052</v>
       </c>
@@ -61817,7 +61837,7 @@
       <c r="Z162" s="10"/>
       <c r="AA162" s="10"/>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>46052</v>
       </c>
@@ -61882,7 +61902,7 @@
       <c r="Z163" s="10"/>
       <c r="AA163" s="10"/>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>46052</v>
       </c>
@@ -61947,7 +61967,7 @@
       <c r="Z164" s="10"/>
       <c r="AA164" s="10"/>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>46052</v>
       </c>
@@ -62012,7 +62032,7 @@
       <c r="Z165" s="10"/>
       <c r="AA165" s="10"/>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>46052</v>
       </c>
@@ -62075,7 +62095,7 @@
       <c r="Z166" s="10"/>
       <c r="AA166" s="10"/>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>46052</v>
       </c>
@@ -62138,7 +62158,7 @@
       <c r="Z167" s="10"/>
       <c r="AA167" s="10"/>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>46052</v>
       </c>
@@ -62201,7 +62221,7 @@
       <c r="Z168" s="10"/>
       <c r="AA168" s="10"/>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>46052</v>
       </c>
@@ -62262,7 +62282,7 @@
       <c r="Z169" s="10"/>
       <c r="AA169" s="10"/>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>46052</v>
       </c>
@@ -62319,7 +62339,7 @@
       <c r="Z170" s="10"/>
       <c r="AA170" s="10"/>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>46052</v>
       </c>
@@ -62374,7 +62394,7 @@
       <c r="Z171" s="10"/>
       <c r="AA171" s="10"/>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>46052</v>
       </c>
@@ -62429,7 +62449,7 @@
       <c r="Z172" s="10"/>
       <c r="AA172" s="10"/>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>46052</v>
       </c>
@@ -62484,7 +62504,7 @@
       <c r="Z173" s="10"/>
       <c r="AA173" s="10"/>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>46052</v>
       </c>
@@ -62543,7 +62563,7 @@
       <c r="Z174" s="10"/>
       <c r="AA174" s="10"/>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>46053</v>
       </c>
@@ -62598,7 +62618,7 @@
       <c r="Z175" s="10"/>
       <c r="AA175" s="10"/>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>46053</v>
       </c>
@@ -62653,7 +62673,7 @@
       <c r="Z176" s="10"/>
       <c r="AA176" s="10"/>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>46053</v>
       </c>
@@ -62708,7 +62728,7 @@
       <c r="Z177" s="10"/>
       <c r="AA177" s="10"/>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>46053</v>
       </c>
@@ -62771,7 +62791,7 @@
       <c r="Z178" s="10"/>
       <c r="AA178" s="10"/>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>46053</v>
       </c>
@@ -62834,7 +62854,7 @@
       <c r="Z179" s="10"/>
       <c r="AA179" s="10"/>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>46053</v>
       </c>
@@ -62895,7 +62915,7 @@
       <c r="Z180" s="10"/>
       <c r="AA180" s="10"/>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>46053</v>
       </c>
@@ -62950,7 +62970,7 @@
       <c r="Z181" s="10"/>
       <c r="AA181" s="10"/>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>46053</v>
       </c>
@@ -63010,7 +63030,7 @@
       <c r="Z182" s="10"/>
       <c r="AA182" s="10"/>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>46053</v>
       </c>
@@ -63071,7 +63091,7 @@
       <c r="Z183" s="10"/>
       <c r="AA183" s="10"/>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>46053</v>
       </c>
@@ -63124,7 +63144,7 @@
       <c r="Z184" s="10"/>
       <c r="AA184" s="10"/>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="L185" t="s">
         <v>58</v>
       </c>
@@ -63132,7 +63152,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="L186">
         <f>SUM(L2:L184)</f>
         <v>315649.30142857111</v>
@@ -63146,14 +63166,20 @@
         <v>1576352.0200000007</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="J187">
         <f>L186+N186</f>
         <v>2257081.7814285709</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA184" xr:uid="{227A76A5-0D02-6F47-A831-12FB6501A393}"/>
+  <autoFilter ref="A1:AA187" xr:uid="{227A76A5-0D02-6F47-A831-12FB6501A393}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="SHIPPING FEE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
